--- a/docs/03. metadata/기관/KOMSA표준단어.xlsx
+++ b/docs/03. metadata/기관/KOMSA표준단어.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -706,6 +706,49 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>정원</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>PSCP</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Personnel Capacity</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>수용 가능한 인원 정원</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>수량</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
